--- a/docs/modelos_importacao/08_Exemplo_Coberturas_TESTE.xlsx
+++ b/docs/modelos_importacao/08_Exemplo_Coberturas_TESTE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia-me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Coberturas'!$A$1:$E$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Coberturas'!$A$1:$E$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Leia-me'!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -523,8 +523,220 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DEMO_NUTRICAO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nutrição e dietética</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Consultas de nutrição com prescrição médica.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{"guaranteeForm":"ANNUAL_PER_PERSON","typicalSublimits":["Até 6 consultas por ano"],"requiresPriorApproval":false}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>COMPLEMENTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DEMO_TERAPIA_FALA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Terapia da fala</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sessões para crianças e adultos.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{"guaranteeForm":"ANNUAL_PER_PERSON","typicalWaitingDays":{"individual":[60,90],"group":[0,30]},"requiresPriorApproval":true}</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>COMPLEMENTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DEMO_PODOLOGIA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Podologia</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Consultas e tratamentos de podologia.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{"exclusions":["Tratamentos estéticos"],"annualLimitAOA":60000}</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>COMPLEMENTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DEMO_ENFERMAGEM_DOMICILIO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Enfermagem ao domicílio</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Cuidados em casa após internamento.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{"allowedCurrencies":["AOA"],"requiresPriorApproval":true,"annualLimitAOA":250000}</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>COMPLEMENTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DEMO_MEDICINA_DESPORTIVA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Medicina desportiva</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avaliação e acompanhamento de lesões desportivas.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>COMPLEMENTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DEMO_SAUDE_MENTAL_ONLINE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Apoio psicológico online</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sessões de psicologia por videochamada.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{"guaranteeForm":"ANNUAL_PER_PERSON","typicalSublimits":["Até 12 sessões por ano"]}</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>COMPLEMENTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DEMO_ACUPUNCTURA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Acupunctura</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sessões com prescrição médica.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{"typicalWaitingDays":{"individual":[90,180],"group":[30,60]},"annualLimitAOA":90000}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>COMPLEMENTAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DEMO_TRANSPORTE_NAO_URGENTE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Transporte não urgente</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Transporte para tratamentos programados.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{"requiresPriorApproval":true,"annualLimitAOA":100000}</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>COMPLEMENTAR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E3"/>
+  <autoFilter ref="A1:E11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
